--- a/data/ExcelParameters/ChannelList.xlsx
+++ b/data/ExcelParameters/ChannelList.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://loreal-my.sharepoint.com/personal/nils_levillain_loreal_com/Documents/Desktop/Python/No Waste Allocation Tool/nw_allocation_tool/data/ExcelParameters/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://loreal-my.sharepoint.com/personal/nils_levillain_loreal_com/Documents/Documents/Cline/nw-allocation-tool/data/ExcelParameters/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DC96C551-B160-4831-A742-9BBFEA777E39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="8_{DC96C551-B160-4831-A742-9BBFEA777E39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{20FE5E61-E9B4-469A-AEFD-420543B54852}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{1DB88EDC-4337-42B5-B70A-9FA86FA323DD}"/>
   </bookViews>
